--- a/Pipeline3App/assets/ButtonsLayout.xlsx
+++ b/Pipeline3App/assets/ButtonsLayout.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Source\Repos\_Openn2\Pipeline2App\assets\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Source\Repos\_Openn2\Pipeline3App\assets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B143FBB7-074F-4383-B4A8-7A2EC02E9A85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C05EBBFF-D6D0-4D25-A8F9-28B62BF3D9B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17790" xr2:uid="{9D6DAE04-F57E-45A2-8B00-3B5708FB93E1}"/>
   </bookViews>
@@ -39,10 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="53">
-  <si>
-    <t>&gt;</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="54">
   <si>
     <t xml:space="preserve">Signals
 Mapping </t>
@@ -131,12 +128,6 @@
     <t>Generate Instances</t>
   </si>
   <si>
-    <t>˅</t>
-  </si>
-  <si>
-    <t>ˇ</t>
-  </si>
-  <si>
     <t>Run Pipeline</t>
   </si>
   <si>
@@ -240,13 +231,25 @@
   <si>
     <t>Open
 Generated Blocks Folder</t>
+  </si>
+  <si>
+    <t>▼</t>
+  </si>
+  <si>
+    <t>→</t>
+  </si>
+  <si>
+    <t>↓</t>
+  </si>
+  <si>
+    <t>—</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -271,6 +274,26 @@
     <font>
       <b/>
       <sz val="11"/>
+      <color theme="1"/>
+      <name val="Courier New"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF00B050"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFFC000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="14"/>
       <color theme="1"/>
       <name val="Courier New"/>
       <family val="3"/>
@@ -350,7 +373,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -384,6 +407,15 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -766,18 +798,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="D1" s="10">
+      <c r="D1" s="12">
         <v>100</v>
       </c>
-      <c r="F1" s="10">
+      <c r="F1" s="12">
         <f>D1+100</f>
         <v>200</v>
       </c>
-      <c r="H1" s="10">
+      <c r="H1" s="12">
         <f>F1+100</f>
         <v>300</v>
       </c>
-      <c r="J1" s="10">
+      <c r="J1" s="13">
         <f>H1+100</f>
         <v>400</v>
       </c>
@@ -805,87 +837,87 @@
     <row r="2" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="3" spans="1:20" ht="45.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B3" s="9" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E3" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="F3" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="G3" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="H3" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="I3" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="J3" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="K3" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="L3" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="F3" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="G3" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="H3" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="I3" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="J3" s="6" t="s">
+      <c r="M3" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="N3" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="O3" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="P3" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="K3" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="L3" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="M3" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="N3" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="O3" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="P3" s="6" t="s">
-        <v>17</v>
-      </c>
       <c r="Q3" s="4" t="s">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="R3" s="6" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="S3" s="4" t="s">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="T3" s="6" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
     </row>
     <row r="4" spans="1:20" x14ac:dyDescent="0.25">
       <c r="D4" s="5" t="s">
-        <v>24</v>
+        <v>50</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>24</v>
+        <v>50</v>
       </c>
       <c r="H4" s="5" t="s">
-        <v>24</v>
+        <v>50</v>
       </c>
       <c r="J4" s="5" t="s">
-        <v>24</v>
+        <v>50</v>
       </c>
       <c r="L4" s="5" t="s">
-        <v>24</v>
+        <v>50</v>
       </c>
       <c r="N4" s="5" t="s">
-        <v>24</v>
+        <v>50</v>
       </c>
       <c r="P4" s="5" t="s">
-        <v>24</v>
+        <v>50</v>
       </c>
       <c r="R4" s="5" t="s">
-        <v>24</v>
+        <v>50</v>
       </c>
       <c r="T4" s="5" t="s">
-        <v>24</v>
+        <v>50</v>
       </c>
     </row>
     <row r="5" spans="1:20" ht="60" x14ac:dyDescent="0.25">
@@ -893,57 +925,61 @@
         <v>10</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J5" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="L5" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="L5" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="N5" s="3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="P5" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="R5" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="T5" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="T5" s="3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="D6" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="J6" s="2"/>
-      <c r="L6" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="N6" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="P6" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="R6" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="T6" s="2"/>
+    </row>
+    <row r="6" spans="1:20" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="D6" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="F6" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="H6" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="J6" s="14" t="s">
+        <v>53</v>
+      </c>
+      <c r="L6" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="N6" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="P6" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="R6" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="T6" s="14" t="s">
+        <v>53</v>
+      </c>
     </row>
     <row r="7" spans="1:20" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="11">
@@ -951,49 +987,61 @@
         <v>20</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F7" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="H7" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="J7" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="L7" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="N7" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="H7" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="J7" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="L7" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="N7" s="3" t="s">
-        <v>51</v>
-      </c>
       <c r="P7" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="R7" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="T7" s="3" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="D8" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="H8" s="2"/>
-      <c r="J8" s="2"/>
-      <c r="L8" s="2"/>
-      <c r="N8" s="2"/>
-      <c r="P8" s="2"/>
-      <c r="R8" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="T8" s="2"/>
+        <v>28</v>
+      </c>
+    </row>
+    <row r="8" spans="1:20" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="D8" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="F8" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="H8" s="14" t="s">
+        <v>53</v>
+      </c>
+      <c r="J8" s="14" t="s">
+        <v>53</v>
+      </c>
+      <c r="L8" s="14" t="s">
+        <v>53</v>
+      </c>
+      <c r="N8" s="14" t="s">
+        <v>53</v>
+      </c>
+      <c r="P8" s="14" t="s">
+        <v>53</v>
+      </c>
+      <c r="R8" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="T8" s="14" t="s">
+        <v>53</v>
+      </c>
     </row>
     <row r="9" spans="1:20" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="11">
@@ -1001,41 +1049,49 @@
         <v>30</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="H9" s="7" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="J9" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="L9" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="L9" s="7" t="s">
+      <c r="N9" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="P9" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="N9" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="P9" s="7" t="s">
-        <v>39</v>
-      </c>
       <c r="R9" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="T9" s="7" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="D10" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="R10" s="2"/>
+        <v>31</v>
+      </c>
+    </row>
+    <row r="10" spans="1:20" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="D10" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="F10" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="L10" s="14" t="s">
+        <v>53</v>
+      </c>
+      <c r="N10" s="14" t="s">
+        <v>53</v>
+      </c>
+      <c r="R10" s="14" t="s">
+        <v>53</v>
+      </c>
     </row>
     <row r="11" spans="1:20" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="11">
@@ -1043,31 +1099,36 @@
         <v>40</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="L11" s="7" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="N11" s="7" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="R11" s="7" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="D12" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="F12" s="2"/>
+        <v>32</v>
+      </c>
+    </row>
+    <row r="12" spans="1:20" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="D12" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="F12" s="14" t="s">
+        <v>53</v>
+      </c>
       <c r="H12" s="2"/>
       <c r="J12" s="2"/>
       <c r="L12" s="2"/>
       <c r="N12" s="2"/>
       <c r="P12" s="2"/>
+      <c r="R12" s="14" t="s">
+        <v>53</v>
+      </c>
       <c r="T12" s="2"/>
     </row>
     <row r="13" spans="1:20" ht="60" customHeight="1" x14ac:dyDescent="0.25">
@@ -1076,10 +1137,10 @@
         <v>50</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="F13" s="7" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="H13" s="2"/>
       <c r="J13" s="2"/>
@@ -1087,12 +1148,17 @@
       <c r="N13" s="2"/>
       <c r="P13" s="2"/>
       <c r="R13" s="7" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="T13" s="2"/>
     </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="D14" s="2"/>
+    <row r="14" spans="1:20" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="D14" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="F14" s="14" t="s">
+        <v>53</v>
+      </c>
       <c r="H14" s="2"/>
       <c r="J14" s="2"/>
       <c r="L14" s="2"/>
@@ -1103,10 +1169,10 @@
     </row>
     <row r="15" spans="1:20" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D15" s="7" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F15" s="7" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="H15" s="2"/>
       <c r="J15" s="2"/>
@@ -1116,8 +1182,13 @@
       <c r="R15" s="2"/>
       <c r="T15" s="2"/>
     </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="D16" s="2"/>
+    <row r="16" spans="1:20" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="D16" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="F16" s="14" t="s">
+        <v>53</v>
+      </c>
       <c r="H16" s="2"/>
       <c r="J16" s="2"/>
       <c r="L16" s="2"/>
@@ -1128,10 +1199,10 @@
     </row>
     <row r="17" spans="4:20" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D17" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="F17" s="7" t="s">
         <v>40</v>
-      </c>
-      <c r="F17" s="7" t="s">
-        <v>43</v>
       </c>
       <c r="H17" s="2"/>
       <c r="J17" s="2"/>
@@ -1141,8 +1212,10 @@
       <c r="R17" s="2"/>
       <c r="T17" s="2"/>
     </row>
-    <row r="18" spans="4:20" x14ac:dyDescent="0.25">
-      <c r="D18" s="2"/>
+    <row r="18" spans="4:20" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="D18" s="14" t="s">
+        <v>53</v>
+      </c>
       <c r="F18" s="2"/>
       <c r="H18" s="2"/>
       <c r="J18" s="2"/>
@@ -1154,7 +1227,7 @@
     </row>
     <row r="19" spans="4:20" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D19" s="7" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="F19" s="2"/>
       <c r="H19" s="2"/>
@@ -1165,8 +1238,10 @@
       <c r="R19" s="2"/>
       <c r="T19" s="2"/>
     </row>
-    <row r="20" spans="4:20" x14ac:dyDescent="0.25">
-      <c r="D20" s="2"/>
+    <row r="20" spans="4:20" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="D20" s="14" t="s">
+        <v>53</v>
+      </c>
       <c r="F20" s="2"/>
       <c r="H20" s="2"/>
       <c r="J20" s="2"/>
@@ -1178,7 +1253,7 @@
     </row>
     <row r="21" spans="4:20" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D21" s="7" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="F21" s="2"/>
       <c r="H21" s="2"/>

--- a/Pipeline3App/assets/ButtonsLayout.xlsx
+++ b/Pipeline3App/assets/ButtonsLayout.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Source\Repos\_Openn2\Pipeline3App\assets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C05EBBFF-D6D0-4D25-A8F9-28B62BF3D9B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{373D4BA7-D120-4549-AC23-00B6F25610F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17790" xr2:uid="{9D6DAE04-F57E-45A2-8B00-3B5708FB93E1}"/>
   </bookViews>
@@ -809,11 +809,11 @@
         <f>F1+100</f>
         <v>300</v>
       </c>
-      <c r="J1" s="13">
+      <c r="J1" s="12">
         <f>H1+100</f>
         <v>400</v>
       </c>
-      <c r="L1" s="10">
+      <c r="L1" s="13">
         <f>J1+100</f>
         <v>500</v>
       </c>

--- a/Pipeline3App/assets/ButtonsLayout.xlsx
+++ b/Pipeline3App/assets/ButtonsLayout.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Source\Repos\_Openn2\Pipeline3App\assets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{373D4BA7-D120-4549-AC23-00B6F25610F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B8B00C2-A122-472E-B9CC-0383493969D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17790" xr2:uid="{9D6DAE04-F57E-45A2-8B00-3B5708FB93E1}"/>
   </bookViews>
@@ -813,19 +813,19 @@
         <f>H1+100</f>
         <v>400</v>
       </c>
-      <c r="L1" s="13">
+      <c r="L1" s="12">
         <f>J1+100</f>
         <v>500</v>
       </c>
-      <c r="N1" s="10">
+      <c r="N1" s="12">
         <f>L1+100</f>
         <v>600</v>
       </c>
-      <c r="P1" s="10">
+      <c r="P1" s="12">
         <f>N1+100</f>
         <v>700</v>
       </c>
-      <c r="R1" s="10">
+      <c r="R1" s="13">
         <f>P1+100</f>
         <v>800</v>
       </c>

--- a/Pipeline3App/assets/ButtonsLayout.xlsx
+++ b/Pipeline3App/assets/ButtonsLayout.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Source\Repos\_Openn2\Pipeline3App\assets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B8B00C2-A122-472E-B9CC-0383493969D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC5E5190-6118-4520-96C6-322529CE8242}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17790" xr2:uid="{9D6DAE04-F57E-45A2-8B00-3B5708FB93E1}"/>
+    <workbookView xWindow="0" yWindow="225" windowWidth="29040" windowHeight="17790" xr2:uid="{9D6DAE04-F57E-45A2-8B00-3B5708FB93E1}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -164,10 +164,6 @@
   </si>
   <si>
     <t>Open
-Empty Shells .xlsm</t>
-  </si>
-  <si>
-    <t>Open
 IO Tags</t>
   </si>
   <si>
@@ -243,6 +239,10 @@
   </si>
   <si>
     <t>—</t>
+  </si>
+  <si>
+    <t>Open
+Builder Shells .xlsm</t>
   </si>
 </sst>
 </file>
@@ -843,49 +843,49 @@
         <v>3</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="F3" s="6" t="s">
         <v>2</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H3" s="6" t="s">
         <v>1</v>
       </c>
       <c r="I3" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="J3" s="6" t="s">
         <v>15</v>
       </c>
       <c r="K3" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="L3" s="6" t="s">
         <v>0</v>
       </c>
       <c r="M3" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="N3" s="6" t="s">
         <v>13</v>
       </c>
       <c r="O3" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="P3" s="6" t="s">
         <v>16</v>
       </c>
       <c r="Q3" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="R3" s="6" t="s">
         <v>19</v>
       </c>
       <c r="S3" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="T3" s="6" t="s">
         <v>23</v>
@@ -893,31 +893,31 @@
     </row>
     <row r="4" spans="1:20" x14ac:dyDescent="0.25">
       <c r="D4" s="5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="H4" s="5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="J4" s="5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="L4" s="5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="N4" s="5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="P4" s="5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="R4" s="5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="T4" s="5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="5" spans="1:20" ht="60" x14ac:dyDescent="0.25">
@@ -928,7 +928,7 @@
         <v>4</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H5" s="3" t="s">
         <v>8</v>
@@ -954,31 +954,31 @@
     </row>
     <row r="6" spans="1:20" ht="18.75" x14ac:dyDescent="0.25">
       <c r="D6" s="14" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F6" s="14" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="H6" s="14" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="J6" s="14" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="L6" s="14" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="N6" s="14" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="P6" s="14" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="R6" s="14" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="T6" s="14" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="7" spans="1:20" ht="60" customHeight="1" x14ac:dyDescent="0.25">
@@ -990,7 +990,7 @@
         <v>5</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="H7" s="3" t="s">
         <v>9</v>
@@ -1002,7 +1002,7 @@
         <v>12</v>
       </c>
       <c r="N7" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="P7" s="3" t="s">
         <v>18</v>
@@ -1016,31 +1016,31 @@
     </row>
     <row r="8" spans="1:20" ht="18.75" x14ac:dyDescent="0.25">
       <c r="D8" s="14" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F8" s="14" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="H8" s="14" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="J8" s="14" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="L8" s="14" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="N8" s="14" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="P8" s="14" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="R8" s="14" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="T8" s="14" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="9" spans="1:20" ht="60" customHeight="1" x14ac:dyDescent="0.25">
@@ -1052,7 +1052,7 @@
         <v>6</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="H9" s="7" t="s">
         <v>25</v>
@@ -1061,13 +1061,13 @@
         <v>30</v>
       </c>
       <c r="L9" s="7" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="N9" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="P9" s="7" t="s">
         <v>35</v>
-      </c>
-      <c r="P9" s="7" t="s">
-        <v>36</v>
       </c>
       <c r="R9" s="3" t="s">
         <v>21</v>
@@ -1078,19 +1078,19 @@
     </row>
     <row r="10" spans="1:20" ht="18.75" x14ac:dyDescent="0.25">
       <c r="D10" s="14" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F10" s="14" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="L10" s="14" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="N10" s="14" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="R10" s="14" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="11" spans="1:20" ht="60" customHeight="1" x14ac:dyDescent="0.25">
@@ -1102,24 +1102,24 @@
         <v>7</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="L11" s="7" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="N11" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="R11" s="7" t="s">
-        <v>32</v>
+        <v>53</v>
       </c>
     </row>
     <row r="12" spans="1:20" ht="18.75" x14ac:dyDescent="0.25">
       <c r="D12" s="14" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F12" s="14" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H12" s="2"/>
       <c r="J12" s="2"/>
@@ -1127,7 +1127,7 @@
       <c r="N12" s="2"/>
       <c r="P12" s="2"/>
       <c r="R12" s="14" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="T12" s="2"/>
     </row>
@@ -1137,10 +1137,10 @@
         <v>50</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F13" s="7" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="H13" s="2"/>
       <c r="J13" s="2"/>
@@ -1148,16 +1148,16 @@
       <c r="N13" s="2"/>
       <c r="P13" s="2"/>
       <c r="R13" s="7" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="T13" s="2"/>
     </row>
     <row r="14" spans="1:20" ht="18.75" x14ac:dyDescent="0.25">
       <c r="D14" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F14" s="14" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H14" s="2"/>
       <c r="J14" s="2"/>
@@ -1172,7 +1172,7 @@
         <v>26</v>
       </c>
       <c r="F15" s="7" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="H15" s="2"/>
       <c r="J15" s="2"/>
@@ -1184,10 +1184,10 @@
     </row>
     <row r="16" spans="1:20" ht="18.75" x14ac:dyDescent="0.25">
       <c r="D16" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F16" s="14" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H16" s="2"/>
       <c r="J16" s="2"/>
@@ -1199,10 +1199,10 @@
     </row>
     <row r="17" spans="4:20" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D17" s="7" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F17" s="7" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="H17" s="2"/>
       <c r="J17" s="2"/>
@@ -1214,7 +1214,7 @@
     </row>
     <row r="18" spans="4:20" ht="18.75" x14ac:dyDescent="0.25">
       <c r="D18" s="14" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F18" s="2"/>
       <c r="H18" s="2"/>
@@ -1227,7 +1227,7 @@
     </row>
     <row r="19" spans="4:20" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D19" s="7" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F19" s="2"/>
       <c r="H19" s="2"/>
@@ -1240,7 +1240,7 @@
     </row>
     <row r="20" spans="4:20" ht="18.75" x14ac:dyDescent="0.25">
       <c r="D20" s="14" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F20" s="2"/>
       <c r="H20" s="2"/>
@@ -1253,7 +1253,7 @@
     </row>
     <row r="21" spans="4:20" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D21" s="7" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F21" s="2"/>
       <c r="H21" s="2"/>

--- a/Pipeline3App/assets/ButtonsLayout.xlsx
+++ b/Pipeline3App/assets/ButtonsLayout.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC5E5190-6118-4520-96C6-322529CE8242}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="225" windowWidth="29040" windowHeight="17790" xr2:uid="{9D6DAE04-F57E-45A2-8B00-3B5708FB93E1}"/>
+    <workbookView xWindow="2340" yWindow="2340" windowWidth="21600" windowHeight="12855" xr2:uid="{9D6DAE04-F57E-45A2-8B00-3B5708FB93E1}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>

--- a/Pipeline3App/assets/ButtonsLayout.xlsx
+++ b/Pipeline3App/assets/ButtonsLayout.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Source\Repos\_Openn2\Pipeline3App\assets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC5E5190-6118-4520-96C6-322529CE8242}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FDDA62AD-64E2-4E92-B165-9DBC90AE6A2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2340" yWindow="2340" windowWidth="21600" windowHeight="12855" xr2:uid="{9D6DAE04-F57E-45A2-8B00-3B5708FB93E1}"/>
   </bookViews>
@@ -373,7 +373,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -401,9 +401,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -798,38 +795,38 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="D1" s="12">
+      <c r="D1" s="11">
         <v>100</v>
       </c>
-      <c r="F1" s="12">
+      <c r="F1" s="11">
         <f>D1+100</f>
         <v>200</v>
       </c>
-      <c r="H1" s="12">
+      <c r="H1" s="11">
         <f>F1+100</f>
         <v>300</v>
       </c>
-      <c r="J1" s="12">
+      <c r="J1" s="11">
         <f>H1+100</f>
         <v>400</v>
       </c>
-      <c r="L1" s="12">
+      <c r="L1" s="11">
         <f>J1+100</f>
         <v>500</v>
       </c>
-      <c r="N1" s="12">
+      <c r="N1" s="11">
         <f>L1+100</f>
         <v>600</v>
       </c>
-      <c r="P1" s="12">
+      <c r="P1" s="11">
         <f>N1+100</f>
         <v>700</v>
       </c>
-      <c r="R1" s="13">
+      <c r="R1" s="11">
         <f>P1+100</f>
         <v>800</v>
       </c>
-      <c r="T1" s="10">
+      <c r="T1" s="12">
         <f>R1+100</f>
         <v>900</v>
       </c>
@@ -921,7 +918,7 @@
       </c>
     </row>
     <row r="5" spans="1:20" ht="60" x14ac:dyDescent="0.25">
-      <c r="A5" s="11">
+      <c r="A5" s="10">
         <v>10</v>
       </c>
       <c r="D5" s="3" t="s">
@@ -953,36 +950,36 @@
       </c>
     </row>
     <row r="6" spans="1:20" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="D6" s="14" t="s">
+      <c r="D6" s="13" t="s">
         <v>51</v>
       </c>
-      <c r="F6" s="14" t="s">
+      <c r="F6" s="13" t="s">
         <v>51</v>
       </c>
-      <c r="H6" s="14" t="s">
+      <c r="H6" s="13" t="s">
         <v>51</v>
       </c>
-      <c r="J6" s="14" t="s">
-        <v>52</v>
-      </c>
-      <c r="L6" s="14" t="s">
+      <c r="J6" s="13" t="s">
+        <v>52</v>
+      </c>
+      <c r="L6" s="13" t="s">
         <v>51</v>
       </c>
-      <c r="N6" s="14" t="s">
+      <c r="N6" s="13" t="s">
         <v>51</v>
       </c>
-      <c r="P6" s="14" t="s">
+      <c r="P6" s="13" t="s">
         <v>51</v>
       </c>
-      <c r="R6" s="14" t="s">
+      <c r="R6" s="13" t="s">
         <v>51</v>
       </c>
-      <c r="T6" s="14" t="s">
+      <c r="T6" s="13" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="7" spans="1:20" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="11">
+      <c r="A7" s="10">
         <f>A5+10</f>
         <v>20</v>
       </c>
@@ -1015,36 +1012,36 @@
       </c>
     </row>
     <row r="8" spans="1:20" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="D8" s="14" t="s">
+      <c r="D8" s="13" t="s">
         <v>51</v>
       </c>
-      <c r="F8" s="14" t="s">
+      <c r="F8" s="13" t="s">
         <v>51</v>
       </c>
-      <c r="H8" s="14" t="s">
-        <v>52</v>
-      </c>
-      <c r="J8" s="14" t="s">
-        <v>52</v>
-      </c>
-      <c r="L8" s="14" t="s">
-        <v>52</v>
-      </c>
-      <c r="N8" s="14" t="s">
-        <v>52</v>
-      </c>
-      <c r="P8" s="14" t="s">
-        <v>52</v>
-      </c>
-      <c r="R8" s="14" t="s">
+      <c r="H8" s="13" t="s">
+        <v>52</v>
+      </c>
+      <c r="J8" s="13" t="s">
+        <v>52</v>
+      </c>
+      <c r="L8" s="13" t="s">
+        <v>52</v>
+      </c>
+      <c r="N8" s="13" t="s">
+        <v>52</v>
+      </c>
+      <c r="P8" s="13" t="s">
+        <v>52</v>
+      </c>
+      <c r="R8" s="13" t="s">
         <v>51</v>
       </c>
-      <c r="T8" s="14" t="s">
+      <c r="T8" s="13" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="9" spans="1:20" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="11">
+      <c r="A9" s="10">
         <f>A7+10</f>
         <v>30</v>
       </c>
@@ -1077,24 +1074,24 @@
       </c>
     </row>
     <row r="10" spans="1:20" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="D10" s="14" t="s">
+      <c r="D10" s="13" t="s">
         <v>51</v>
       </c>
-      <c r="F10" s="14" t="s">
+      <c r="F10" s="13" t="s">
         <v>51</v>
       </c>
-      <c r="L10" s="14" t="s">
-        <v>52</v>
-      </c>
-      <c r="N10" s="14" t="s">
-        <v>52</v>
-      </c>
-      <c r="R10" s="14" t="s">
+      <c r="L10" s="13" t="s">
+        <v>52</v>
+      </c>
+      <c r="N10" s="13" t="s">
+        <v>52</v>
+      </c>
+      <c r="R10" s="13" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="11" spans="1:20" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="11">
+      <c r="A11" s="10">
         <f>A9+10</f>
         <v>40</v>
       </c>
@@ -1115,10 +1112,10 @@
       </c>
     </row>
     <row r="12" spans="1:20" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="D12" s="14" t="s">
+      <c r="D12" s="13" t="s">
         <v>51</v>
       </c>
-      <c r="F12" s="14" t="s">
+      <c r="F12" s="13" t="s">
         <v>52</v>
       </c>
       <c r="H12" s="2"/>
@@ -1126,13 +1123,13 @@
       <c r="L12" s="2"/>
       <c r="N12" s="2"/>
       <c r="P12" s="2"/>
-      <c r="R12" s="14" t="s">
+      <c r="R12" s="13" t="s">
         <v>52</v>
       </c>
       <c r="T12" s="2"/>
     </row>
     <row r="13" spans="1:20" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="11">
+      <c r="A13" s="10">
         <f>A11+10</f>
         <v>50</v>
       </c>
@@ -1156,7 +1153,7 @@
       <c r="D14" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="F14" s="14" t="s">
+      <c r="F14" s="13" t="s">
         <v>52</v>
       </c>
       <c r="H14" s="2"/>
@@ -1186,7 +1183,7 @@
       <c r="D16" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="F16" s="14" t="s">
+      <c r="F16" s="13" t="s">
         <v>52</v>
       </c>
       <c r="H16" s="2"/>
@@ -1213,7 +1210,7 @@
       <c r="T17" s="2"/>
     </row>
     <row r="18" spans="4:20" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="D18" s="14" t="s">
+      <c r="D18" s="13" t="s">
         <v>52</v>
       </c>
       <c r="F18" s="2"/>
@@ -1239,7 +1236,7 @@
       <c r="T19" s="2"/>
     </row>
     <row r="20" spans="4:20" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="D20" s="14" t="s">
+      <c r="D20" s="13" t="s">
         <v>52</v>
       </c>
       <c r="F20" s="2"/>
